--- a/Template 2.xlsx
+++ b/Template 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://puprtes-my.sharepoint.com/personal/ramadhan_alchandra_yasrial_pu_go_id/Documents/PU/Task/2026/Oktober/SPRIN dan ND Penugasan/Create/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://puprtes-my.sharepoint.com/personal/ramadhan_alchandra_yasrial_pu_go_id/Documents/PU/pu-code/scripts/create_mutasi_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="11_AD4D066CA252ABDACC1048FF99DE7BEC5BDEDCC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91092098-792D-491F-AABF-A0ABE25809E0}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="11_AD4D066CA252ABDACC1048FF99DE7BEC5BDEDCC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB75333-E8F2-4D62-B0D1-D769164CC6B6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>No</t>
   </si>
@@ -76,13 +76,16 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +118,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -184,6 +195,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -371,14 +385,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>401706</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>161096</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>124238</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1068456</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>4969</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>69656</xdr:rowOff>
+      <xdr:rowOff>69655</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -395,8 +409,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6522554" y="3507270"/>
-          <a:ext cx="1909141" cy="1813560"/>
+          <a:off x="6522554" y="3528390"/>
+          <a:ext cx="1756741" cy="1469417"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -561,10 +575,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -833,7 +843,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -933,9 +943,25 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
